--- a/Configs/事件event.xlsx
+++ b/Configs/事件event.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="事件event_config" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="501">
   <si>
     <t>id</t>
   </si>
@@ -311,66 +311,39 @@
     <t>击退</t>
   </si>
   <si>
-    <t>击退目标力度50%</t>
-  </si>
-  <si>
-    <t>击退目标力度55%</t>
-  </si>
-  <si>
-    <t>击退目标力度60%</t>
+    <t>击退目标力度</t>
   </si>
   <si>
     <t>6000</t>
   </si>
   <si>
-    <t>击退目标力度65%</t>
-  </si>
-  <si>
-    <t>6500</t>
-  </si>
-  <si>
-    <t>击退目标力度70%</t>
-  </si>
-  <si>
     <t>7000</t>
   </si>
   <si>
-    <t>击退目标力度75%</t>
-  </si>
-  <si>
-    <t>7500</t>
-  </si>
-  <si>
-    <t>击退目标力度80%</t>
-  </si>
-  <si>
     <t>8000</t>
   </si>
   <si>
-    <t>击退目标力度85%</t>
-  </si>
-  <si>
-    <t>8500</t>
-  </si>
-  <si>
-    <t>击退目标力度90%</t>
-  </si>
-  <si>
     <t>9000</t>
   </si>
   <si>
-    <t>击退目标力度95%</t>
-  </si>
-  <si>
-    <t>9500</t>
-  </si>
-  <si>
-    <t>击退目标力度100%</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
     <t>经验</t>
   </si>
   <si>
@@ -1130,13 +1103,13 @@
     <t>弹射5次</t>
   </si>
   <si>
-    <t>5|3000|0|8000</t>
+    <t>5|8000</t>
   </si>
   <si>
     <t>弹射15次</t>
   </si>
   <si>
-    <t>15|3000|0|8000</t>
+    <t>15|8000</t>
   </si>
   <si>
     <t>弹射 10</t>
@@ -1145,7 +1118,7 @@
     <t>弹射15次，伤害不衰减</t>
   </si>
   <si>
-    <t>15|10000|0|10000</t>
+    <t>15|10000</t>
   </si>
   <si>
     <t>连射 1</t>
@@ -3374,10 +3347,10 @@
         <v>92</v>
       </c>
       <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3396,10 +3369,10 @@
         <v>92</v>
       </c>
       <c r="E40" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3418,10 +3391,10 @@
         <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3440,10 +3413,10 @@
         <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3462,10 +3435,10 @@
         <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3484,10 +3457,10 @@
         <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3506,10 +3479,10 @@
         <v>92</v>
       </c>
       <c r="E45" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3528,10 +3501,10 @@
         <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3550,10 +3523,10 @@
         <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3572,10 +3545,10 @@
         <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3590,13 +3563,13 @@
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3612,13 +3585,13 @@
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3634,13 +3607,13 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3656,13 +3629,13 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3678,13 +3651,13 @@
         <v>5</v>
       </c>
       <c r="D53" t="s">
+        <v>104</v>
+      </c>
+      <c r="E53" t="s">
         <v>113</v>
       </c>
-      <c r="E53" t="s">
-        <v>122</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3700,13 +3673,13 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3722,13 +3695,13 @@
         <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3744,13 +3717,13 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3766,13 +3739,13 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E57" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3788,13 +3761,13 @@
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3809,13 +3782,13 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -3831,13 +3804,13 @@
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -3853,13 +3826,13 @@
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E61" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -3875,13 +3848,13 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -3897,13 +3870,13 @@
         <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -3919,13 +3892,13 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E64" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3941,13 +3914,13 @@
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E65" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3963,13 +3936,13 @@
         <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3985,13 +3958,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E67" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -4007,13 +3980,13 @@
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E68" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4029,13 +4002,13 @@
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E69" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4051,13 +4024,13 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E70" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4073,13 +4046,13 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4095,13 +4068,13 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -4117,13 +4090,13 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4139,13 +4112,13 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E74" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4161,13 +4134,13 @@
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E75" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -4183,13 +4156,13 @@
         <v>18</v>
       </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -4205,13 +4178,13 @@
         <v>19</v>
       </c>
       <c r="D77" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E77" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -4227,13 +4200,13 @@
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E78" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -4249,13 +4222,13 @@
         <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E79" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -4271,13 +4244,13 @@
         <v>22</v>
       </c>
       <c r="D80" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E80" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -4293,13 +4266,13 @@
         <v>23</v>
       </c>
       <c r="D81" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E81" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -4315,13 +4288,13 @@
         <v>24</v>
       </c>
       <c r="D82" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E82" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -4337,13 +4310,13 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E83" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -4359,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -4381,13 +4354,13 @@
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E85" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -4403,13 +4376,13 @@
         <v>28</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E86" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -4425,13 +4398,13 @@
         <v>29</v>
       </c>
       <c r="D87" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E87" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -4447,13 +4420,13 @@
         <v>30</v>
       </c>
       <c r="D88" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E88" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -4469,13 +4442,13 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -4491,13 +4464,13 @@
         <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E90" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -4513,13 +4486,13 @@
         <v>33</v>
       </c>
       <c r="D91" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4535,13 +4508,13 @@
         <v>34</v>
       </c>
       <c r="D92" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E92" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -4557,13 +4530,13 @@
         <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E93" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -4579,13 +4552,13 @@
         <v>36</v>
       </c>
       <c r="D94" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4601,13 +4574,13 @@
         <v>37</v>
       </c>
       <c r="D95" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E95" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4623,13 +4596,13 @@
         <v>38</v>
       </c>
       <c r="D96" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4645,13 +4618,13 @@
         <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E97" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -4667,13 +4640,13 @@
         <v>40</v>
       </c>
       <c r="D98" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="E98" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4688,10 +4661,10 @@
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E99" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F99" s="4">
         <v>1000</v>
@@ -4710,10 +4683,10 @@
         <v>200</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E100" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>42</v>
@@ -4732,10 +4705,10 @@
         <v>201</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E101" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F101" s="4">
         <v>2001</v>
@@ -4754,10 +4727,10 @@
         <v>202</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E102" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F102" s="4">
         <v>2002</v>
@@ -4776,10 +4749,10 @@
         <v>203</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E103" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F103" s="4">
         <v>2003</v>
@@ -4798,10 +4771,10 @@
         <v>204</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E104" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F104" s="4">
         <v>2004</v>
@@ -4820,10 +4793,10 @@
         <v>205</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E105" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F105" s="4">
         <v>2005</v>
@@ -4842,10 +4815,10 @@
         <v>206</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E106" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="F106" s="4">
         <v>2006</v>
@@ -4864,10 +4837,10 @@
         <v>207</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E107" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F107" s="4">
         <v>2007</v>
@@ -4886,10 +4859,10 @@
         <v>208</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>265</v>
       </c>
       <c r="F108" s="4">
         <v>2008</v>
@@ -4908,10 +4881,10 @@
         <v>209</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E109" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F109" s="4">
         <v>2009</v>
@@ -4930,10 +4903,10 @@
         <v>210</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E110" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F110" s="4">
         <v>2010</v>
@@ -4952,10 +4925,10 @@
         <v>211</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E111" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F111" s="4">
         <v>2011</v>
@@ -4974,10 +4947,10 @@
         <v>212</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E112" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F112" s="4">
         <v>2012</v>
@@ -4996,10 +4969,10 @@
         <v>213</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E113" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F113" s="4">
         <v>2013</v>
@@ -5018,13 +4991,13 @@
         <v>214</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E114" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5039,13 +5012,13 @@
         <v>300</v>
       </c>
       <c r="D115" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E115" t="s">
-        <v>274</v>
-      </c>
-      <c r="F115" s="4">
-        <v>2016</v>
+        <v>265</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5061,10 +5034,10 @@
         <v>301</v>
       </c>
       <c r="D116" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E116" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F116" s="3">
         <v>3001</v>
@@ -5082,10 +5055,10 @@
         <v>400</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F117" s="3">
         <v>4000</v>
@@ -5103,10 +5076,10 @@
         <v>500</v>
       </c>
       <c r="D118" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E118" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F118" s="3">
         <v>5000</v>
@@ -5124,10 +5097,10 @@
         <v>600</v>
       </c>
       <c r="D119" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E119" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="F119" s="3">
         <v>6000</v>
@@ -5146,13 +5119,13 @@
         <v>601</v>
       </c>
       <c r="D120" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E120" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5167,13 +5140,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E121" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5188,13 +5161,13 @@
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E122" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5209,13 +5182,13 @@
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E123" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5230,10 +5203,10 @@
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F124" s="3">
         <v>1001</v>
@@ -5251,13 +5224,13 @@
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5273,13 +5246,13 @@
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E126" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5295,13 +5268,13 @@
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E127" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5317,13 +5290,13 @@
         <v>4</v>
       </c>
       <c r="D128" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E128" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5339,13 +5312,13 @@
         <v>5</v>
       </c>
       <c r="D129" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E129" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5361,13 +5334,13 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E130" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5383,13 +5356,13 @@
         <v>7</v>
       </c>
       <c r="D131" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E131" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5405,13 +5378,13 @@
         <v>8</v>
       </c>
       <c r="D132" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E132" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5427,13 +5400,13 @@
         <v>9</v>
       </c>
       <c r="D133" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E133" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -5449,13 +5422,13 @@
         <v>10</v>
       </c>
       <c r="D134" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E134" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -5470,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E135" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5491,10 +5464,10 @@
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E136" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>18</v>
@@ -5561,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F3">
         <v>999</v>
@@ -5582,13 +5555,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E4" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5603,13 +5576,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F5" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5624,13 +5597,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5645,13 +5618,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E7" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:6">
@@ -5663,13 +5636,13 @@
         <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E8" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5684,13 +5657,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E9" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F9" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5705,13 +5678,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E10" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F10" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5726,13 +5699,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F11" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5747,13 +5720,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E12" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5768,13 +5741,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E13" t="s">
+        <v>337</v>
+      </c>
+      <c r="F13" t="s">
         <v>346</v>
-      </c>
-      <c r="F13" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5789,13 +5762,13 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="E14" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F14" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5810,13 +5783,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E15" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F15" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -5831,13 +5804,13 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E16" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F16" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5852,13 +5825,13 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E17" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F17" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5873,13 +5846,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E18" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F18" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5894,13 +5867,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E19" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F19" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5915,13 +5888,13 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E20" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="F20" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5936,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E21" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -5957,10 +5930,10 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="E22" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -5978,10 +5951,10 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E23" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -5999,10 +5972,10 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="E24" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -6020,10 +5993,10 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E25" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -6041,10 +6014,10 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="E26" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -6062,10 +6035,10 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E27" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="F27">
         <v>7</v>
@@ -6083,10 +6056,10 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E28" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -6104,10 +6077,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E29" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -6125,10 +6098,10 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E30" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -6146,13 +6119,13 @@
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="E31" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="F31" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -6167,13 +6140,13 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E32" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F32" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -6188,13 +6161,13 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="E33" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F33" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -6209,13 +6182,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E34" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F34" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -6230,13 +6203,13 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E35" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F35" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -6251,13 +6224,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E36" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F36" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -6272,13 +6245,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="E37" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F37" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -6293,13 +6266,13 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E38" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F38" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -6314,13 +6287,13 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="E39" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F39" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:6">
@@ -6332,10 +6305,10 @@
         <v>301</v>
       </c>
       <c r="D40" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E40" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:6">
@@ -6347,10 +6320,10 @@
         <v>302</v>
       </c>
       <c r="D41" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -6383,49 +6356,49 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1" t="s">
+        <v>415</v>
+      </c>
+      <c r="H1" t="s">
+        <v>416</v>
+      </c>
+      <c r="I1" t="s">
+        <v>417</v>
+      </c>
+      <c r="J1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>419</v>
+      </c>
+      <c r="M1" t="s">
         <v>420</v>
       </c>
-      <c r="D1" t="s">
+      <c r="N1" t="s">
         <v>421</v>
       </c>
-      <c r="E1" t="s">
+      <c r="O1" t="s">
         <v>422</v>
       </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
         <v>423</v>
       </c>
-      <c r="G1" t="s">
+      <c r="Q1" t="s">
         <v>424</v>
-      </c>
-      <c r="H1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I1" t="s">
-        <v>426</v>
-      </c>
-      <c r="J1" t="s">
-        <v>427</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" t="s">
-        <v>428</v>
-      </c>
-      <c r="M1" t="s">
-        <v>429</v>
-      </c>
-      <c r="N1" t="s">
-        <v>430</v>
-      </c>
-      <c r="O1" t="s">
-        <v>431</v>
-      </c>
-      <c r="P1" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -6466,10 +6439,10 @@
         <v>5</v>
       </c>
       <c r="M2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="N2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="O2" t="s">
         <v>7</v>
@@ -6478,7 +6451,7 @@
         <v>7</v>
       </c>
       <c r="Q2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -6486,13 +6459,13 @@
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -6507,10 +6480,10 @@
         <v>1000</v>
       </c>
       <c r="I3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -6519,19 +6492,19 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N3" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="O3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -6539,13 +6512,13 @@
         <v>2000</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -6560,10 +6533,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -6572,19 +6545,19 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q4" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -6593,13 +6566,13 @@
         <v>2001</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -6614,10 +6587,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -6626,19 +6599,19 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q5" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -6647,13 +6620,13 @@
         <v>2002</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6668,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -6680,19 +6653,19 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q6" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -6701,13 +6674,13 @@
         <v>2003</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -6722,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -6734,19 +6707,19 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q7" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -6755,13 +6728,13 @@
         <v>2004</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -6776,10 +6749,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -6788,19 +6761,19 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q8" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -6809,13 +6782,13 @@
         <v>2005</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6830,10 +6803,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -6842,19 +6815,19 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q9" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -6863,13 +6836,13 @@
         <v>2006</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -6884,10 +6857,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -6896,19 +6869,19 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P10" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q10" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -6917,13 +6890,13 @@
         <v>2007</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -6938,10 +6911,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -6950,19 +6923,19 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q11" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -6971,13 +6944,13 @@
         <v>2008</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6992,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -7004,19 +6977,19 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q12" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -7025,13 +6998,13 @@
         <v>2009</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D13" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -7046,10 +7019,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -7058,19 +7031,19 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P13" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q13" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -7079,13 +7052,13 @@
         <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D14" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -7100,10 +7073,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -7112,19 +7085,19 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P14" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q14" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -7133,13 +7106,13 @@
         <v>2011</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D15" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -7154,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -7166,19 +7139,19 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q15" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -7187,13 +7160,13 @@
         <v>2012</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -7208,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -7220,19 +7193,19 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P16" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q16" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -7241,13 +7214,13 @@
         <v>2013</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D17" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -7262,10 +7235,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K17">
         <v>2</v>
@@ -7274,19 +7247,19 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P17" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q17" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -7295,13 +7268,13 @@
         <v>2014</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -7316,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -7328,19 +7301,19 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P18" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q18" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -7348,13 +7321,13 @@
         <v>3000</v>
       </c>
       <c r="B19" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -7369,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -7381,19 +7354,19 @@
         <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="N19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q19" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -7402,13 +7375,13 @@
         <v>3001</v>
       </c>
       <c r="B20" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -7423,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K20">
         <v>2</v>
@@ -7435,19 +7408,19 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="N20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q20" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:17">
@@ -7455,13 +7428,13 @@
         <v>4000</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D21" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -7476,10 +7449,10 @@
         <v>1000</v>
       </c>
       <c r="I21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -7488,16 +7461,16 @@
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O21">
         <v>10012</v>
       </c>
       <c r="P21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q21" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:17">
@@ -7505,13 +7478,13 @@
         <v>5000</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -7526,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -7538,16 +7511,16 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="N22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -7555,13 +7528,13 @@
         <v>6000</v>
       </c>
       <c r="B23" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D23" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -7576,10 +7549,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K23">
         <v>2</v>
@@ -7588,19 +7561,19 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="N23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -7608,13 +7581,13 @@
         <v>6001</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D24" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -7629,10 +7602,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -7641,19 +7614,19 @@
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="N24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q24" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -7661,13 +7634,13 @@
         <v>7000</v>
       </c>
       <c r="B25" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D25" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -7682,10 +7655,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -7694,19 +7667,19 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P25" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q25" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -7715,13 +7688,13 @@
         <v>7001</v>
       </c>
       <c r="B26" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D26" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -7736,10 +7709,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -7748,19 +7721,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P26" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q26" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -7769,13 +7742,13 @@
         <v>7002</v>
       </c>
       <c r="B27" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D27" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -7790,10 +7763,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -7802,19 +7775,19 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P27" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q27" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -7823,13 +7796,13 @@
         <v>7003</v>
       </c>
       <c r="B28" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D28" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -7844,10 +7817,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -7856,19 +7829,19 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P28" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q28" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -7877,13 +7850,13 @@
         <v>7004</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D29" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -7898,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -7910,19 +7883,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P29" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q29" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -7931,13 +7904,13 @@
         <v>7005</v>
       </c>
       <c r="B30" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D30" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -7952,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -7964,19 +7937,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q30" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -7985,13 +7958,13 @@
         <v>7006</v>
       </c>
       <c r="B31" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D31" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -8006,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8018,19 +7991,19 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P31" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q31" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -8039,13 +8012,13 @@
         <v>7007</v>
       </c>
       <c r="B32" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D32" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -8060,10 +8033,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -8072,19 +8045,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q32" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -8093,13 +8066,13 @@
         <v>7008</v>
       </c>
       <c r="B33" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="C33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D33" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -8114,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -8126,19 +8099,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P33" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q33" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -8147,13 +8120,13 @@
         <v>7009</v>
       </c>
       <c r="B34" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D34" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -8168,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -8180,19 +8153,19 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P34" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q34" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -8200,13 +8173,13 @@
         <v>8000</v>
       </c>
       <c r="B35" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D35" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -8221,10 +8194,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8233,19 +8206,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="N35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Q35" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -8274,34 +8247,34 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="F1" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="G1" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="H1" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="I1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="J1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="K1" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="L1" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -8327,7 +8300,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="I2" t="s">
         <v>5</v>
@@ -8347,10 +8320,10 @@
         <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="F3">
         <v>105</v>

--- a/Configs/事件event.xlsx
+++ b/Configs/事件event.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="事件event_config" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="509">
   <si>
     <t>id</t>
   </si>
@@ -1533,6 +1533,30 @@
   </si>
   <si>
     <t>对所有敌人造成击退，并且恢复自身已损失生命值的50%</t>
+  </si>
+  <si>
+    <t>狂热过载 I</t>
+  </si>
+  <si>
+    <t>攻击时有10%概率连射5枚过载弹，每颗造成20%火伤</t>
+  </si>
+  <si>
+    <t>狂热过载 II</t>
+  </si>
+  <si>
+    <t>攻击时有10%概率连射10枚过载弹，每颗造成20%火伤</t>
+  </si>
+  <si>
+    <t>狂热过载 III</t>
+  </si>
+  <si>
+    <t>攻击时有20%概率连射10枚过载弹，每颗造成20%火伤</t>
+  </si>
+  <si>
+    <t>狂热过载 IV</t>
+  </si>
+  <si>
+    <t>攻击时有20%概率连射10枚过载弹，每颗造成20%火伤，命中后发生2次散射</t>
   </si>
 </sst>
 </file>
@@ -2146,10 +2170,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2506,7 +2533,7 @@
     <col min="3" max="3" width="9.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="44.25" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3"/>
+    <col min="6" max="6" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2522,7 +2549,7 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2539,12 +2566,12 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <f t="shared" ref="A3:A19" si="0">10000*B3+C3</f>
         <v>10001</v>
       </c>
@@ -2560,12 +2587,12 @@
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>10002</v>
       </c>
@@ -2582,12 +2609,12 @@
       <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>10003</v>
       </c>
@@ -2604,12 +2631,12 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>10004</v>
       </c>
@@ -2626,12 +2653,12 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>10005</v>
       </c>
@@ -2648,12 +2675,12 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>10006</v>
       </c>
@@ -2670,12 +2697,12 @@
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>10007</v>
       </c>
@@ -2692,12 +2719,12 @@
       <c r="E9" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>10008</v>
       </c>
@@ -2714,12 +2741,12 @@
       <c r="E10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10009</v>
       </c>
@@ -2736,12 +2763,12 @@
       <c r="E11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10010</v>
       </c>
@@ -2758,12 +2785,12 @@
       <c r="E12" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>10011</v>
       </c>
@@ -2780,12 +2807,12 @@
       <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>10012</v>
       </c>
@@ -2802,19 +2829,19 @@
       <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>20001</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>1</v>
       </c>
       <c r="D15" t="s">
@@ -2823,19 +2850,19 @@
       <c r="E15" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>20002</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <f t="shared" ref="C16:C24" si="2">C15+1</f>
         <v>2</v>
       </c>
@@ -2845,19 +2872,19 @@
       <c r="E16" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>20003</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -2867,19 +2894,19 @@
       <c r="E17" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>20004</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -2889,19 +2916,19 @@
       <c r="E18" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>20005</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -2911,19 +2938,19 @@
       <c r="E19" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <f t="shared" ref="A20:A37" si="3">10000*B20+C20</f>
         <v>20006</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -2933,19 +2960,19 @@
       <c r="E20" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <f t="shared" si="3"/>
         <v>20007</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2955,19 +2982,19 @@
       <c r="E21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <f t="shared" si="3"/>
         <v>20008</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2977,19 +3004,19 @@
       <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <f t="shared" si="3"/>
         <v>20009</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2999,19 +3026,19 @@
       <c r="E23" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <f t="shared" si="3"/>
         <v>20010</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -3021,12 +3048,12 @@
       <c r="E24" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <f t="shared" si="3"/>
         <v>30001</v>
       </c>
@@ -3042,12 +3069,12 @@
       <c r="E25" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <f t="shared" si="3"/>
         <v>30002</v>
       </c>
@@ -3064,12 +3091,12 @@
       <c r="E26" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <f t="shared" si="3"/>
         <v>30003</v>
       </c>
@@ -3086,12 +3113,12 @@
       <c r="E27" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <f t="shared" si="3"/>
         <v>30004</v>
       </c>
@@ -3108,12 +3135,12 @@
       <c r="E28" t="s">
         <v>73</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <f t="shared" si="3"/>
         <v>30005</v>
       </c>
@@ -3130,12 +3157,12 @@
       <c r="E29" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <f t="shared" si="3"/>
         <v>30006</v>
       </c>
@@ -3152,12 +3179,12 @@
       <c r="E30" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <f t="shared" si="3"/>
         <v>30007</v>
       </c>
@@ -3174,12 +3201,12 @@
       <c r="E31" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <f t="shared" si="3"/>
         <v>30008</v>
       </c>
@@ -3196,12 +3223,12 @@
       <c r="E32" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <f t="shared" si="3"/>
         <v>30009</v>
       </c>
@@ -3218,12 +3245,12 @@
       <c r="E33" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <f t="shared" si="3"/>
         <v>30010</v>
       </c>
@@ -3240,12 +3267,12 @@
       <c r="E34" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <f t="shared" si="3"/>
         <v>30011</v>
       </c>
@@ -3262,12 +3289,12 @@
       <c r="E35" t="s">
         <v>87</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <f t="shared" si="3"/>
         <v>30012</v>
       </c>
@@ -3284,12 +3311,12 @@
       <c r="E36" t="s">
         <v>89</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <f t="shared" si="3"/>
         <v>30013</v>
       </c>
@@ -3306,19 +3333,19 @@
       <c r="E37" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <f t="shared" ref="A38:A80" si="5">10000*B38+C38</f>
         <v>40001</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>1</v>
       </c>
       <c r="D38" t="s">
@@ -3327,19 +3354,19 @@
       <c r="E38" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <f t="shared" si="5"/>
         <v>40002</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <f t="shared" ref="C39:C48" si="6">C38+1</f>
         <v>2</v>
       </c>
@@ -3349,19 +3376,19 @@
       <c r="E39" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <f t="shared" si="5"/>
         <v>40003</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -3371,19 +3398,19 @@
       <c r="E40" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <f t="shared" si="5"/>
         <v>40004</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
@@ -3393,19 +3420,19 @@
       <c r="E41" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <f t="shared" si="5"/>
         <v>40005</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
@@ -3415,19 +3442,19 @@
       <c r="E42" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <f t="shared" si="5"/>
         <v>40006</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -3437,19 +3464,19 @@
       <c r="E43" t="s">
         <v>93</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <f t="shared" si="5"/>
         <v>40007</v>
       </c>
       <c r="B44">
         <v>4</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="3">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
@@ -3459,19 +3486,19 @@
       <c r="E44" t="s">
         <v>93</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <f t="shared" si="5"/>
         <v>40008</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
@@ -3481,19 +3508,19 @@
       <c r="E45" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <f t="shared" si="5"/>
         <v>40009</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
@@ -3503,19 +3530,19 @@
       <c r="E46" t="s">
         <v>93</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <f t="shared" si="5"/>
         <v>40010</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
@@ -3525,19 +3552,19 @@
       <c r="E47" t="s">
         <v>93</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <f t="shared" si="5"/>
         <v>40011</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
@@ -3547,12 +3574,12 @@
       <c r="E48" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <f t="shared" si="5"/>
         <v>50001</v>
       </c>
@@ -3568,19 +3595,19 @@
       <c r="E49" t="s">
         <v>105</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <f t="shared" si="5"/>
         <v>50002</v>
       </c>
       <c r="B50">
         <v>5</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3">
         <f t="shared" ref="C50:C58" si="7">C49+1</f>
         <v>2</v>
       </c>
@@ -3590,19 +3617,19 @@
       <c r="E50" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <f t="shared" si="5"/>
         <v>50003</v>
       </c>
       <c r="B51">
         <v>5</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -3612,19 +3639,19 @@
       <c r="E51" t="s">
         <v>109</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <f t="shared" si="5"/>
         <v>50004</v>
       </c>
       <c r="B52">
         <v>5</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="3">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -3634,19 +3661,19 @@
       <c r="E52" t="s">
         <v>111</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <f t="shared" si="5"/>
         <v>50005</v>
       </c>
       <c r="B53">
         <v>5</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -3656,19 +3683,19 @@
       <c r="E53" t="s">
         <v>113</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <f t="shared" si="5"/>
         <v>50006</v>
       </c>
       <c r="B54">
         <v>5</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -3678,19 +3705,19 @@
       <c r="E54" t="s">
         <v>115</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <f t="shared" si="5"/>
         <v>50007</v>
       </c>
       <c r="B55">
         <v>5</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
@@ -3700,19 +3727,19 @@
       <c r="E55" t="s">
         <v>117</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <f t="shared" si="5"/>
         <v>50008</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="3">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
@@ -3722,19 +3749,19 @@
       <c r="E56" t="s">
         <v>119</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <f t="shared" si="5"/>
         <v>50009</v>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="3">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
@@ -3744,19 +3771,19 @@
       <c r="E57" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <f t="shared" si="5"/>
         <v>50010</v>
       </c>
       <c r="B58">
         <v>5</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="3">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
@@ -3766,19 +3793,19 @@
       <c r="E58" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <f t="shared" si="5"/>
         <v>60001</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>1</v>
       </c>
       <c r="D59" t="s">
@@ -3787,19 +3814,19 @@
       <c r="E59" t="s">
         <v>126</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <f t="shared" si="5"/>
         <v>60002</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="3">
         <f t="shared" ref="C59:C97" si="8">C59+1</f>
         <v>2</v>
       </c>
@@ -3809,19 +3836,19 @@
       <c r="E60" t="s">
         <v>129</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <f t="shared" si="5"/>
         <v>60003</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="3">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
@@ -3831,19 +3858,19 @@
       <c r="E61" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <f t="shared" si="5"/>
         <v>60004</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="3">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
@@ -3853,19 +3880,19 @@
       <c r="E62" t="s">
         <v>135</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <f t="shared" si="5"/>
         <v>60005</v>
       </c>
       <c r="B63">
         <v>6</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="3">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
@@ -3875,19 +3902,19 @@
       <c r="E63" t="s">
         <v>138</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <f t="shared" si="5"/>
         <v>60006</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="3">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
@@ -3897,19 +3924,19 @@
       <c r="E64" t="s">
         <v>141</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <f t="shared" si="5"/>
         <v>60007</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="3">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
@@ -3919,19 +3946,19 @@
       <c r="E65" t="s">
         <v>144</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <f t="shared" si="5"/>
         <v>60008</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="3">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
@@ -3941,19 +3968,19 @@
       <c r="E66" t="s">
         <v>147</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <f t="shared" si="5"/>
         <v>60009</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
@@ -3963,19 +3990,19 @@
       <c r="E67" t="s">
         <v>150</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <f t="shared" si="5"/>
         <v>60010</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="3">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -3985,19 +4012,19 @@
       <c r="E68" t="s">
         <v>153</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <f t="shared" si="5"/>
         <v>60011</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="3">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
@@ -4007,19 +4034,19 @@
       <c r="E69" t="s">
         <v>156</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <f t="shared" si="5"/>
         <v>60012</v>
       </c>
       <c r="B70">
         <v>6</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="3">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
@@ -4029,19 +4056,19 @@
       <c r="E70" t="s">
         <v>159</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <f t="shared" si="5"/>
         <v>60013</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="3">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
@@ -4051,19 +4078,19 @@
       <c r="E71" t="s">
         <v>162</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <f t="shared" si="5"/>
         <v>60014</v>
       </c>
       <c r="B72">
         <v>6</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="3">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -4073,19 +4100,19 @@
       <c r="E72" t="s">
         <v>165</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <f t="shared" si="5"/>
         <v>60015</v>
       </c>
       <c r="B73">
         <v>6</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="3">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
@@ -4095,19 +4122,19 @@
       <c r="E73" t="s">
         <v>168</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <f t="shared" si="5"/>
         <v>60016</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="3">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
@@ -4117,19 +4144,19 @@
       <c r="E74" t="s">
         <v>171</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <f t="shared" si="5"/>
         <v>60017</v>
       </c>
       <c r="B75">
         <v>6</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="3">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
@@ -4139,19 +4166,19 @@
       <c r="E75" t="s">
         <v>174</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <f t="shared" si="5"/>
         <v>60018</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="3">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
@@ -4161,19 +4188,19 @@
       <c r="E76" t="s">
         <v>177</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <f t="shared" si="5"/>
         <v>60019</v>
       </c>
       <c r="B77">
         <v>6</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="3">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
@@ -4183,19 +4210,19 @@
       <c r="E77" t="s">
         <v>180</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <f t="shared" si="5"/>
         <v>60020</v>
       </c>
       <c r="B78">
         <v>6</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="3">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
@@ -4205,19 +4232,19 @@
       <c r="E78" t="s">
         <v>183</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <f t="shared" si="5"/>
         <v>60021</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="3">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
@@ -4227,19 +4254,19 @@
       <c r="E79" t="s">
         <v>186</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <f t="shared" si="5"/>
         <v>60022</v>
       </c>
       <c r="B80">
         <v>6</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="3">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
@@ -4249,19 +4276,19 @@
       <c r="E80" t="s">
         <v>189</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="4" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <f t="shared" ref="A81:A96" si="9">10000*B81+C81</f>
         <v>60023</v>
       </c>
       <c r="B81">
         <v>6</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="3">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
@@ -4271,19 +4298,19 @@
       <c r="E81" t="s">
         <v>192</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <f t="shared" si="9"/>
         <v>60024</v>
       </c>
       <c r="B82">
         <v>6</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="3">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
@@ -4293,19 +4320,19 @@
       <c r="E82" t="s">
         <v>195</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="4" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <f t="shared" si="9"/>
         <v>60025</v>
       </c>
       <c r="B83">
         <v>6</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="3">
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
@@ -4315,19 +4342,19 @@
       <c r="E83" t="s">
         <v>198</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="4" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <f t="shared" si="9"/>
         <v>60026</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="3">
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
@@ -4337,19 +4364,19 @@
       <c r="E84" t="s">
         <v>201</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <f t="shared" si="9"/>
         <v>60027</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="3">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
@@ -4359,19 +4386,19 @@
       <c r="E85" t="s">
         <v>204</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="4" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <f t="shared" si="9"/>
         <v>60028</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="3">
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
@@ -4381,19 +4408,19 @@
       <c r="E86" t="s">
         <v>207</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <f t="shared" si="9"/>
         <v>60029</v>
       </c>
       <c r="B87">
         <v>6</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="3">
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
@@ -4403,19 +4430,19 @@
       <c r="E87" t="s">
         <v>210</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <f t="shared" si="9"/>
         <v>60030</v>
       </c>
       <c r="B88">
         <v>6</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88" s="3">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
@@ -4425,19 +4452,19 @@
       <c r="E88" t="s">
         <v>213</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <f t="shared" si="9"/>
         <v>60031</v>
       </c>
       <c r="B89">
         <v>6</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="3">
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
@@ -4447,19 +4474,19 @@
       <c r="E89" t="s">
         <v>216</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <f t="shared" si="9"/>
         <v>60032</v>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="3">
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
@@ -4469,19 +4496,19 @@
       <c r="E90" t="s">
         <v>219</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <f t="shared" si="9"/>
         <v>60033</v>
       </c>
       <c r="B91">
         <v>6</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="3">
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
@@ -4491,19 +4518,19 @@
       <c r="E91" t="s">
         <v>222</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <f t="shared" si="9"/>
         <v>60034</v>
       </c>
       <c r="B92">
         <v>6</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="3">
         <f t="shared" si="8"/>
         <v>34</v>
       </c>
@@ -4513,19 +4540,19 @@
       <c r="E92" t="s">
         <v>225</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <f t="shared" si="9"/>
         <v>60035</v>
       </c>
       <c r="B93">
         <v>6</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="3">
         <f t="shared" si="8"/>
         <v>35</v>
       </c>
@@ -4535,19 +4562,19 @@
       <c r="E93" t="s">
         <v>228</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="4" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <f t="shared" si="9"/>
         <v>60036</v>
       </c>
       <c r="B94">
         <v>6</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="3">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
@@ -4557,19 +4584,19 @@
       <c r="E94" t="s">
         <v>231</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="4" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <f t="shared" si="9"/>
         <v>60037</v>
       </c>
       <c r="B95">
         <v>6</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="3">
         <f t="shared" si="8"/>
         <v>37</v>
       </c>
@@ -4579,19 +4606,19 @@
       <c r="E95" t="s">
         <v>234</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <f t="shared" si="9"/>
         <v>60038</v>
       </c>
       <c r="B96">
         <v>6</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="3">
         <f t="shared" si="8"/>
         <v>38</v>
       </c>
@@ -4601,19 +4628,19 @@
       <c r="E96" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <f t="shared" ref="A97:A108" si="10">10000*B97+C97</f>
         <v>60039</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="3">
         <f t="shared" si="8"/>
         <v>39</v>
       </c>
@@ -4623,19 +4650,19 @@
       <c r="E97" t="s">
         <v>240</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <f t="shared" si="10"/>
         <v>60040</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="3">
         <f t="shared" ref="C98:C115" si="11">C97+1</f>
         <v>40</v>
       </c>
@@ -4645,19 +4672,19 @@
       <c r="E98" t="s">
         <v>243</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="4" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <f t="shared" si="10"/>
         <v>70010</v>
       </c>
       <c r="B99">
         <v>7</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="3">
         <v>10</v>
       </c>
       <c r="D99" t="s">
@@ -4666,349 +4693,349 @@
       <c r="E99" t="s">
         <v>246</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <f t="shared" si="10"/>
         <v>70200</v>
       </c>
       <c r="B100">
         <v>7</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="3">
         <f>200</f>
         <v>200</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E100" t="s">
         <v>248</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <f t="shared" si="10"/>
         <v>70201</v>
       </c>
       <c r="B101">
         <v>7</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="3">
         <f t="shared" si="11"/>
         <v>201</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E101" t="s">
         <v>249</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="5">
         <v>2001</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <f t="shared" si="10"/>
         <v>70202</v>
       </c>
       <c r="B102">
         <v>7</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102" s="3">
         <f t="shared" si="11"/>
         <v>202</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E102" t="s">
         <v>250</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="5">
         <v>2002</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <f t="shared" si="10"/>
         <v>70203</v>
       </c>
       <c r="B103">
         <v>7</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="3">
         <f t="shared" si="11"/>
         <v>203</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E103" t="s">
         <v>251</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="5">
         <v>2003</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <f t="shared" si="10"/>
         <v>70204</v>
       </c>
       <c r="B104">
         <v>7</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="3">
         <f t="shared" si="11"/>
         <v>204</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E104" t="s">
         <v>252</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="5">
         <v>2004</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="2">
+      <c r="A105" s="3">
         <f t="shared" si="10"/>
         <v>70205</v>
       </c>
       <c r="B105">
         <v>7</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="3">
         <f t="shared" si="11"/>
         <v>205</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E105" t="s">
         <v>253</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="5">
         <v>2005</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="2">
+      <c r="A106" s="3">
         <f t="shared" si="10"/>
         <v>70206</v>
       </c>
       <c r="B106">
         <v>7</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="3">
         <f t="shared" si="11"/>
         <v>206</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E106" t="s">
         <v>254</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="5">
         <v>2006</v>
       </c>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="2">
+      <c r="A107" s="3">
         <f t="shared" si="10"/>
         <v>70207</v>
       </c>
       <c r="B107">
         <v>7</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="3">
         <f t="shared" si="11"/>
         <v>207</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E107" t="s">
         <v>255</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="5">
         <v>2007</v>
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="2">
+      <c r="A108" s="3">
         <f t="shared" si="10"/>
         <v>70208</v>
       </c>
       <c r="B108">
         <v>7</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="3">
         <f t="shared" si="11"/>
         <v>208</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E108" t="s">
         <v>256</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="5">
         <v>2008</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="2">
+      <c r="A109" s="3">
         <f t="shared" ref="A109:A115" si="12">10000*B109+C109</f>
         <v>70209</v>
       </c>
       <c r="B109">
         <v>7</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="3">
         <f t="shared" si="11"/>
         <v>209</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E109" t="s">
         <v>257</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="5">
         <v>2009</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="2">
+      <c r="A110" s="3">
         <f t="shared" si="12"/>
         <v>70210</v>
       </c>
       <c r="B110">
         <v>7</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="3">
         <f t="shared" si="11"/>
         <v>210</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E110" t="s">
         <v>258</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="5">
         <v>2010</v>
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="2">
+      <c r="A111" s="3">
         <f t="shared" si="12"/>
         <v>70211</v>
       </c>
       <c r="B111">
         <v>7</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="3">
         <f t="shared" si="11"/>
         <v>211</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E111" t="s">
         <v>259</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="5">
         <v>2011</v>
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="2">
+      <c r="A112" s="3">
         <f t="shared" si="12"/>
         <v>70212</v>
       </c>
       <c r="B112">
         <v>7</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="3">
         <f t="shared" si="11"/>
         <v>212</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E112" t="s">
         <v>260</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="5">
         <v>2012</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="2">
+      <c r="A113" s="3">
         <f t="shared" si="12"/>
         <v>70213</v>
       </c>
       <c r="B113">
         <v>7</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="3">
         <f t="shared" si="11"/>
         <v>213</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E113" t="s">
         <v>261</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="5">
         <v>2013</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="2">
+      <c r="A114" s="3">
         <f t="shared" si="12"/>
         <v>70214</v>
       </c>
       <c r="B114">
         <v>7</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114" s="3">
         <f t="shared" si="11"/>
         <v>214</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="3" t="s">
         <v>247</v>
       </c>
       <c r="E114" t="s">
         <v>262</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="5" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="2">
+      <c r="A115" s="3">
         <f t="shared" ref="A115:A120" si="13">10000*B115+C115</f>
         <v>70300</v>
       </c>
       <c r="B115">
         <v>7</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="3">
         <v>300</v>
       </c>
       <c r="D115" t="s">
@@ -5017,19 +5044,19 @@
       <c r="E115" t="s">
         <v>265</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="2">
+      <c r="A116" s="3">
         <f t="shared" si="13"/>
         <v>70301</v>
       </c>
       <c r="B116">
         <v>7</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="3">
         <f>C115+1</f>
         <v>301</v>
       </c>
@@ -5039,19 +5066,19 @@
       <c r="E116" t="s">
         <v>267</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="4">
         <v>3001</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="2">
+      <c r="A117" s="3">
         <f t="shared" si="13"/>
         <v>70400</v>
       </c>
       <c r="B117">
         <v>7</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="3">
         <v>400</v>
       </c>
       <c r="D117" t="s">
@@ -5060,19 +5087,19 @@
       <c r="E117" t="s">
         <v>269</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="4">
         <v>4000</v>
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="2">
+      <c r="A118" s="3">
         <f t="shared" si="13"/>
         <v>70500</v>
       </c>
       <c r="B118">
         <v>7</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="3">
         <v>500</v>
       </c>
       <c r="D118" t="s">
@@ -5081,19 +5108,19 @@
       <c r="E118" t="s">
         <v>271</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="2">
+      <c r="A119" s="3">
         <f t="shared" si="13"/>
         <v>70600</v>
       </c>
       <c r="B119">
         <v>7</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="3">
         <v>600</v>
       </c>
       <c r="D119" t="s">
@@ -5102,19 +5129,19 @@
       <c r="E119" t="s">
         <v>273</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="4">
         <v>6000</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="2">
+      <c r="A120" s="3">
         <f t="shared" si="13"/>
         <v>70601</v>
       </c>
       <c r="B120">
         <v>7</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="3">
         <f>C119+1</f>
         <v>601</v>
       </c>
@@ -5124,19 +5151,19 @@
       <c r="E120" t="s">
         <v>274</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="4" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="2">
+      <c r="A121" s="3">
         <f t="shared" ref="A121:A123" si="14">10000*B121+C121</f>
         <v>70001</v>
       </c>
       <c r="B121">
         <v>7</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="3">
         <v>1</v>
       </c>
       <c r="D121" t="s">
@@ -5145,19 +5172,19 @@
       <c r="E121" t="s">
         <v>277</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="4" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="2">
+      <c r="A122" s="3">
         <f t="shared" si="14"/>
         <v>70002</v>
       </c>
       <c r="B122">
         <v>7</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="3">
         <v>2</v>
       </c>
       <c r="D122" t="s">
@@ -5166,19 +5193,19 @@
       <c r="E122" t="s">
         <v>279</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="4" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="2">
+      <c r="A123" s="3">
         <f t="shared" si="14"/>
         <v>70002</v>
       </c>
       <c r="B123">
         <v>7</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="3">
         <v>2</v>
       </c>
       <c r="D123" t="s">
@@ -5187,19 +5214,19 @@
       <c r="E123" t="s">
         <v>281</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="4" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="2">
+      <c r="A124" s="3">
         <f t="shared" ref="A124:A136" si="15">10000*B124+C124</f>
         <v>80001</v>
       </c>
       <c r="B124">
         <v>8</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="3">
         <v>1</v>
       </c>
       <c r="D124" t="s">
@@ -5208,19 +5235,19 @@
       <c r="E124" t="s">
         <v>284</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="4">
         <v>1001</v>
       </c>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="2">
+      <c r="A125" s="3">
         <f t="shared" si="15"/>
         <v>90001</v>
       </c>
       <c r="B125">
         <v>9</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="3">
         <v>1</v>
       </c>
       <c r="D125" t="s">
@@ -5229,19 +5256,19 @@
       <c r="E125" t="s">
         <v>286</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="4" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="2">
+      <c r="A126" s="3">
         <f t="shared" si="15"/>
         <v>90002</v>
       </c>
       <c r="B126">
         <v>9</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="3">
         <f t="shared" ref="C126:C134" si="16">C125+1</f>
         <v>2</v>
       </c>
@@ -5251,19 +5278,19 @@
       <c r="E126" t="s">
         <v>289</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="4" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="2">
+      <c r="A127" s="3">
         <f t="shared" si="15"/>
         <v>90003</v>
       </c>
       <c r="B127">
         <v>9</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="3">
         <f t="shared" si="16"/>
         <v>3</v>
       </c>
@@ -5273,19 +5300,19 @@
       <c r="E127" t="s">
         <v>292</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="4" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="2">
+      <c r="A128" s="3">
         <f t="shared" si="15"/>
         <v>90004</v>
       </c>
       <c r="B128">
         <v>9</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="3">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
@@ -5295,19 +5322,19 @@
       <c r="E128" t="s">
         <v>295</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="4" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="2">
+      <c r="A129" s="3">
         <f t="shared" si="15"/>
         <v>90005</v>
       </c>
       <c r="B129">
         <v>9</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="3">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
@@ -5317,19 +5344,19 @@
       <c r="E129" t="s">
         <v>298</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="4" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="2">
+      <c r="A130" s="3">
         <f t="shared" si="15"/>
         <v>90006</v>
       </c>
       <c r="B130">
         <v>9</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="3">
         <f t="shared" si="16"/>
         <v>6</v>
       </c>
@@ -5339,19 +5366,19 @@
       <c r="E130" t="s">
         <v>301</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="4" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="2">
+      <c r="A131" s="3">
         <f t="shared" si="15"/>
         <v>90007</v>
       </c>
       <c r="B131">
         <v>9</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="3">
         <f t="shared" si="16"/>
         <v>7</v>
       </c>
@@ -5361,19 +5388,19 @@
       <c r="E131" t="s">
         <v>304</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="4" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="2">
+      <c r="A132" s="3">
         <f t="shared" si="15"/>
         <v>90008</v>
       </c>
       <c r="B132">
         <v>9</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="3">
         <f t="shared" si="16"/>
         <v>8</v>
       </c>
@@ -5383,19 +5410,19 @@
       <c r="E132" t="s">
         <v>307</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="4" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="2">
+      <c r="A133" s="3">
         <f t="shared" si="15"/>
         <v>90009</v>
       </c>
       <c r="B133">
         <v>9</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="3">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
@@ -5405,19 +5432,19 @@
       <c r="E133" t="s">
         <v>310</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="4" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="2">
+      <c r="A134" s="3">
         <f t="shared" si="15"/>
         <v>90010</v>
       </c>
       <c r="B134">
         <v>9</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="3">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
@@ -5427,19 +5454,19 @@
       <c r="E134" t="s">
         <v>313</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="4" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="2">
+      <c r="A135" s="3">
         <f t="shared" si="15"/>
         <v>100001</v>
       </c>
       <c r="B135">
         <v>10</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="3">
         <v>1</v>
       </c>
       <c r="D135" t="s">
@@ -5448,12 +5475,12 @@
       <c r="E135" t="s">
         <v>316</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="4" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="2">
+      <c r="A136" s="3">
         <f t="shared" si="15"/>
         <v>110001</v>
       </c>
@@ -5469,7 +5496,7 @@
       <c r="E136" t="s">
         <v>319</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5653,7 +5680,7 @@
       <c r="B9">
         <v>201</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>2</v>
       </c>
       <c r="D9" t="s">
@@ -5674,7 +5701,7 @@
       <c r="B10">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>3</v>
       </c>
       <c r="D10" t="s">
@@ -5695,7 +5722,7 @@
       <c r="B11">
         <v>201</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" t="s">
@@ -5716,7 +5743,7 @@
       <c r="B12">
         <v>201</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5</v>
       </c>
       <c r="D12" t="s">
@@ -5737,7 +5764,7 @@
       <c r="B13">
         <v>201</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6</v>
       </c>
       <c r="D13" t="s">
@@ -5758,7 +5785,7 @@
       <c r="B14">
         <v>201</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>7</v>
       </c>
       <c r="D14" t="s">
@@ -5779,7 +5806,7 @@
       <c r="B15">
         <v>201</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>8</v>
       </c>
       <c r="D15" t="s">
@@ -5800,7 +5827,7 @@
       <c r="B16">
         <v>201</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>9</v>
       </c>
       <c r="D16" t="s">
@@ -5821,7 +5848,7 @@
       <c r="B17">
         <v>201</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>10</v>
       </c>
       <c r="D17" t="s">
@@ -5835,14 +5862,14 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>202001</v>
       </c>
       <c r="B18">
         <v>202</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>1</v>
       </c>
       <c r="D18" t="s">
@@ -5856,14 +5883,14 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>202002</v>
       </c>
       <c r="B19">
         <v>202</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>2</v>
       </c>
       <c r="D19" t="s">
@@ -5877,14 +5904,14 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>202003</v>
       </c>
       <c r="B20">
         <v>202</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>3</v>
       </c>
       <c r="D20" t="s">
@@ -5898,11 +5925,11 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>203001</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>203</v>
       </c>
       <c r="C21">
@@ -5919,14 +5946,14 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>203002</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>203</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>2</v>
       </c>
       <c r="D22" t="s">
@@ -5940,14 +5967,14 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>203003</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>203</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>3</v>
       </c>
       <c r="D23" t="s">
@@ -5961,14 +5988,14 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>203004</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>203</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>4</v>
       </c>
       <c r="D24" t="s">
@@ -5982,14 +6009,14 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>203005</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>203</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>5</v>
       </c>
       <c r="D25" t="s">
@@ -6003,14 +6030,14 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>203006</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>203</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>6</v>
       </c>
       <c r="D26" t="s">
@@ -6024,14 +6051,14 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>203007</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>203</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>7</v>
       </c>
       <c r="D27" t="s">
@@ -6045,14 +6072,14 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>203008</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>203</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>8</v>
       </c>
       <c r="D28" t="s">
@@ -6066,14 +6093,14 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>203009</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>203</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3">
         <v>9</v>
       </c>
       <c r="D29" t="s">
@@ -6087,14 +6114,14 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>203010</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>203</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>10</v>
       </c>
       <c r="D30" t="s">
@@ -6108,14 +6135,14 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>204002</v>
       </c>
       <c r="B31">
         <v>204</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>2</v>
       </c>
       <c r="D31" t="s">
@@ -6129,14 +6156,14 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>204003</v>
       </c>
       <c r="B32">
         <v>204</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>3</v>
       </c>
       <c r="D32" t="s">
@@ -6150,14 +6177,14 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>204004</v>
       </c>
       <c r="B33">
         <v>204</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="3">
         <v>4</v>
       </c>
       <c r="D33" t="s">
@@ -6171,14 +6198,14 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>204005</v>
       </c>
       <c r="B34">
         <v>204</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>5</v>
       </c>
       <c r="D34" t="s">
@@ -6192,14 +6219,14 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>204006</v>
       </c>
       <c r="B35">
         <v>204</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="3">
         <v>6</v>
       </c>
       <c r="D35" t="s">
@@ -6213,14 +6240,14 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>204007</v>
       </c>
       <c r="B36">
         <v>204</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="3">
         <v>7</v>
       </c>
       <c r="D36" t="s">
@@ -6234,14 +6261,14 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>204008</v>
       </c>
       <c r="B37">
         <v>204</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3">
         <v>8</v>
       </c>
       <c r="D37" t="s">
@@ -6255,14 +6282,14 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>204009</v>
       </c>
       <c r="B38">
         <v>204</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>9</v>
       </c>
       <c r="D38" t="s">
@@ -6276,14 +6303,14 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>204010</v>
       </c>
       <c r="B39">
         <v>204</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <v>10</v>
       </c>
       <c r="D39" t="s">
@@ -6297,7 +6324,7 @@
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:6">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>301000</v>
       </c>
@@ -6312,7 +6339,7 @@
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:6">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>302000</v>
       </c>
@@ -8230,114 +8257,200 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="5" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="23.75" customWidth="1"/>
-    <col min="9" max="10" width="7.375" customWidth="1"/>
-    <col min="12" max="12" width="46.75" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="34.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="1" customWidth="1"/>
+    <col min="9" max="10" width="7.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="46.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:12">
-      <c r="A3">
+    <row r="3" s="1" customFormat="1" ht="27" spans="1:12">
+      <c r="A3" s="1">
         <v>1001</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>105</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1001</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>10000</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1000401</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" ht="27" spans="1:12">
+      <c r="A4" s="1">
+        <v>4011</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F4" s="1">
+        <v>502</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4001001</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:12">
+      <c r="A5" s="1">
+        <v>4012</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F5" s="1">
+        <v>502</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K5" s="1">
+        <v>4001002</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:12">
+      <c r="A6" s="1">
+        <v>4013</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F6" s="1">
+        <v>502</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>4001002</v>
+      </c>
+    </row>
+    <row r="7" ht="27" spans="1:12">
+      <c r="A7" s="1">
+        <v>4014</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F7" s="1">
+        <v>502</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4001003</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
